--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,6 +1645,452 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121823522</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>586239</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6317283</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121825782</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>586084</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6317446</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121823985</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Råsnäs 1:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>586203</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6317316</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121822806</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>586237</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6317277</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1647,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121823522</v>
+        <v>121823985</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,52 +1659,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586239</v>
+        <v>586203</v>
       </c>
       <c r="R9" t="n">
-        <v>6317283</v>
+        <v>6317316</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1763,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121825782</v>
+        <v>121822806</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,31 +1766,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586084</v>
+        <v>586237</v>
       </c>
       <c r="R10" t="n">
-        <v>6317446</v>
+        <v>6317277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121823985</v>
+        <v>121823522</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,43 +1882,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586203</v>
+        <v>586239</v>
       </c>
       <c r="R11" t="n">
-        <v>6317316</v>
+        <v>6317283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1977,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121822806</v>
+        <v>121825782</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1989,40 +1998,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586237</v>
+        <v>586084</v>
       </c>
       <c r="R12" t="n">
-        <v>6317277</v>
+        <v>6317446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1647,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121823985</v>
+        <v>121822806</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,43 +1659,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586203</v>
+        <v>586237</v>
       </c>
       <c r="R9" t="n">
-        <v>6317316</v>
+        <v>6317277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1754,10 +1763,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121822806</v>
+        <v>121823985</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1766,52 +1775,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586237</v>
+        <v>586203</v>
       </c>
       <c r="R10" t="n">
-        <v>6317277</v>
+        <v>6317316</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121823522</v>
+        <v>121825782</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,40 +1882,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1924,10 +1915,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586239</v>
+        <v>586084</v>
       </c>
       <c r="R11" t="n">
-        <v>6317283</v>
+        <v>6317446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1986,10 +1977,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121825782</v>
+        <v>121823522</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1998,31 +1989,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586084</v>
+        <v>586239</v>
       </c>
       <c r="R12" t="n">
-        <v>6317446</v>
+        <v>6317283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1647,7 +1647,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121822806</v>
+        <v>121823522</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586237</v>
+        <v>586239</v>
       </c>
       <c r="R9" t="n">
-        <v>6317277</v>
+        <v>6317283</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121823985</v>
+        <v>121825782</v>
       </c>
       <c r="B10" t="n">
         <v>57373</v>
@@ -1799,19 +1799,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586203</v>
+        <v>586084</v>
       </c>
       <c r="R10" t="n">
-        <v>6317316</v>
+        <v>6317446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121825782</v>
+        <v>121822806</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,31 +1882,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1915,10 +1924,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586084</v>
+        <v>586237</v>
       </c>
       <c r="R11" t="n">
-        <v>6317446</v>
+        <v>6317277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1977,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121823522</v>
+        <v>121823985</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1989,52 +1998,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586239</v>
+        <v>586203</v>
       </c>
       <c r="R12" t="n">
-        <v>6317283</v>
+        <v>6317316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1647,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121823522</v>
+        <v>121825782</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,40 +1659,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1701,10 +1692,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586239</v>
+        <v>586084</v>
       </c>
       <c r="R9" t="n">
-        <v>6317283</v>
+        <v>6317446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1763,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121825782</v>
+        <v>121823522</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,31 +1766,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586084</v>
+        <v>586239</v>
       </c>
       <c r="R10" t="n">
-        <v>6317446</v>
+        <v>6317283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121822806</v>
+        <v>121823985</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,52 +1882,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586237</v>
+        <v>586203</v>
       </c>
       <c r="R11" t="n">
-        <v>6317277</v>
+        <v>6317316</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1986,10 +1977,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121823985</v>
+        <v>121822806</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1998,43 +1989,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586203</v>
+        <v>586237</v>
       </c>
       <c r="R12" t="n">
-        <v>6317316</v>
+        <v>6317277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121823985</v>
+        <v>121822806</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,43 +1882,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586203</v>
+        <v>586237</v>
       </c>
       <c r="R11" t="n">
-        <v>6317316</v>
+        <v>6317277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1977,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121822806</v>
+        <v>121823985</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1989,52 +1998,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586237</v>
+        <v>586203</v>
       </c>
       <c r="R12" t="n">
-        <v>6317277</v>
+        <v>6317316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2090,6 +2090,128 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121838432</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56577</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råsnäs 1.1, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>586051</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6317455</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121825782</v>
+        <v>121823985</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1683,19 +1683,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586084</v>
+        <v>586203</v>
       </c>
       <c r="R9" t="n">
-        <v>6317446</v>
+        <v>6317316</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1757,7 +1757,7 @@
         <v>121823522</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121822806</v>
+        <v>121825782</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,40 +1882,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1924,10 +1915,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586237</v>
+        <v>586084</v>
       </c>
       <c r="R11" t="n">
-        <v>6317277</v>
+        <v>6317446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1986,10 +1977,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121823985</v>
+        <v>121822806</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>98131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1998,43 +1989,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586203</v>
+        <v>586237</v>
       </c>
       <c r="R12" t="n">
-        <v>6317316</v>
+        <v>6317277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2213,6 +2213,815 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122037739</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>586272</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6317286</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122037669</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>586190</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6317402</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122022216</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>586328</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6317238</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122021993</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>586192</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6317434</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122037687</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>586183</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6317427</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122021281</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Råsnäs 1.1, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>585956</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6317492</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122021641</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>586088</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6317479</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3022,6 +3022,128 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122058487</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56577</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Råsnäs 1:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>586239</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6317322</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122022216</v>
+        <v>122021993</v>
       </c>
       <c r="B16" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2469,52 +2469,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586328</v>
+        <v>586192</v>
       </c>
       <c r="R16" t="n">
-        <v>6317238</v>
+        <v>6317434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2573,10 +2564,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122021993</v>
+        <v>122022216</v>
       </c>
       <c r="B17" t="n">
-        <v>57381</v>
+        <v>98131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2585,43 +2576,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586192</v>
+        <v>586328</v>
       </c>
       <c r="R17" t="n">
-        <v>6317434</v>
+        <v>6317238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1754,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121823522</v>
+        <v>121822806</v>
       </c>
       <c r="B10" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586239</v>
+        <v>586237</v>
       </c>
       <c r="R10" t="n">
-        <v>6317283</v>
+        <v>6317277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121825782</v>
+        <v>121823522</v>
       </c>
       <c r="B11" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,31 +1882,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1915,10 +1924,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586084</v>
+        <v>586239</v>
       </c>
       <c r="R11" t="n">
-        <v>6317446</v>
+        <v>6317283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1977,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121822806</v>
+        <v>121825782</v>
       </c>
       <c r="B12" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1989,40 +1998,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586237</v>
+        <v>586084</v>
       </c>
       <c r="R12" t="n">
-        <v>6317277</v>
+        <v>6317446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122037739</v>
+        <v>122021281</v>
       </c>
       <c r="B14" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2250,26 +2250,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586272</v>
+        <v>585956</v>
       </c>
       <c r="R14" t="n">
-        <v>6317286</v>
+        <v>6317492</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2296,50 +2302,39 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122037669</v>
+        <v>122021993</v>
       </c>
       <c r="B15" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2348,49 +2343,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586190</v>
+        <v>586192</v>
       </c>
       <c r="R15" t="n">
-        <v>6317402</v>
+        <v>6317434</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2417,50 +2409,39 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122021993</v>
+        <v>122037669</v>
       </c>
       <c r="B16" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2469,46 +2450,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586192</v>
+        <v>586190</v>
       </c>
       <c r="R16" t="n">
-        <v>6317434</v>
+        <v>6317402</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2535,29 +2519,40 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2567,7 +2562,7 @@
         <v>122022216</v>
       </c>
       <c r="B17" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2683,7 +2678,7 @@
         <v>122037687</v>
       </c>
       <c r="B18" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2801,10 +2796,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122021281</v>
+        <v>122021641</v>
       </c>
       <c r="B19" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2813,52 +2808,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585956</v>
+        <v>586088</v>
       </c>
       <c r="R19" t="n">
-        <v>6317492</v>
+        <v>6317479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2917,10 +2903,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122021641</v>
+        <v>122037739</v>
       </c>
       <c r="B20" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2929,46 +2915,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586088</v>
+        <v>586272</v>
       </c>
       <c r="R20" t="n">
-        <v>6317479</v>
+        <v>6317286</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2995,29 +2984,40 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1647,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121823522</v>
+        <v>121825782</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,40 +1659,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1701,10 +1692,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586239</v>
+        <v>586084</v>
       </c>
       <c r="R9" t="n">
-        <v>6317283</v>
+        <v>6317446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1763,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121822806</v>
+        <v>121823985</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,52 +1766,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586237</v>
+        <v>586203</v>
       </c>
       <c r="R10" t="n">
-        <v>6317277</v>
+        <v>6317316</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1879,10 +1861,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121825782</v>
+        <v>121823522</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1891,31 +1873,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1924,10 +1915,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586084</v>
+        <v>586239</v>
       </c>
       <c r="R11" t="n">
-        <v>6317446</v>
+        <v>6317283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1986,10 +1977,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121823985</v>
+        <v>121822806</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1998,43 +1989,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586203</v>
+        <v>586237</v>
       </c>
       <c r="R12" t="n">
-        <v>6317316</v>
+        <v>6317277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021993</v>
+        <v>122022216</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2227,43 +2227,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586192</v>
+        <v>586328</v>
       </c>
       <c r="R14" t="n">
-        <v>6317434</v>
+        <v>6317238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2322,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122037669</v>
+        <v>122021993</v>
       </c>
       <c r="B15" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2334,49 +2343,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586190</v>
+        <v>586192</v>
       </c>
       <c r="R15" t="n">
-        <v>6317402</v>
+        <v>6317434</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2403,47 +2409,36 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122022216</v>
+        <v>122037687</v>
       </c>
       <c r="B16" t="n">
         <v>98175</v>
@@ -2478,32 +2473,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586328</v>
+        <v>586183</v>
       </c>
       <c r="R16" t="n">
-        <v>6317238</v>
+        <v>6317427</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2530,29 +2519,40 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122037687</v>
+        <v>122037669</v>
       </c>
       <c r="B19" t="n">
         <v>98175</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586183</v>
+        <v>586190</v>
       </c>
       <c r="R19" t="n">
-        <v>6317427</v>
+        <v>6317402</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -2215,10 +2215,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122022216</v>
+        <v>122021641</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2227,52 +2227,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586328</v>
+        <v>586088</v>
       </c>
       <c r="R14" t="n">
-        <v>6317238</v>
+        <v>6317479</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2438,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122037687</v>
+        <v>122037669</v>
       </c>
       <c r="B16" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,7 +2464,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2486,10 +2477,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586183</v>
+        <v>586190</v>
       </c>
       <c r="R16" t="n">
-        <v>6317427</v>
+        <v>6317402</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2562,7 +2553,7 @@
         <v>122037739</v>
       </c>
       <c r="B17" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2680,10 +2671,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122021281</v>
+        <v>122037687</v>
       </c>
       <c r="B18" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2715,32 +2706,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585956</v>
+        <v>586183</v>
       </c>
       <c r="R18" t="n">
-        <v>6317492</v>
+        <v>6317427</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,39 +2752,50 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122037669</v>
+        <v>122021281</v>
       </c>
       <c r="B19" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2831,26 +2827,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586190</v>
+        <v>585956</v>
       </c>
       <c r="R19" t="n">
-        <v>6317402</v>
+        <v>6317492</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2877,50 +2879,39 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122021641</v>
+        <v>122022216</v>
       </c>
       <c r="B20" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2929,43 +2920,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586088</v>
+        <v>586328</v>
       </c>
       <c r="R20" t="n">
-        <v>6317479</v>
+        <v>6317238</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -2215,10 +2215,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021641</v>
+        <v>122037669</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2227,46 +2227,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586088</v>
+        <v>586190</v>
       </c>
       <c r="R14" t="n">
-        <v>6317479</v>
+        <v>6317402</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2293,39 +2296,50 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021993</v>
+        <v>122037687</v>
       </c>
       <c r="B15" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2334,46 +2348,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586192</v>
+        <v>586183</v>
       </c>
       <c r="R15" t="n">
-        <v>6317434</v>
+        <v>6317427</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2400,36 +2417,47 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122037669</v>
+        <v>122022216</v>
       </c>
       <c r="B16" t="n">
         <v>98185</v>
@@ -2464,26 +2492,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586190</v>
+        <v>586328</v>
       </c>
       <c r="R16" t="n">
-        <v>6317402</v>
+        <v>6317238</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2510,40 +2544,29 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2671,10 +2694,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122037687</v>
+        <v>122021993</v>
       </c>
       <c r="B18" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2683,49 +2706,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586183</v>
+        <v>586192</v>
       </c>
       <c r="R18" t="n">
-        <v>6317427</v>
+        <v>6317434</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2752,50 +2772,39 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122021281</v>
+        <v>122021641</v>
       </c>
       <c r="B19" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2804,52 +2813,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585956</v>
+        <v>586088</v>
       </c>
       <c r="R19" t="n">
-        <v>6317492</v>
+        <v>6317479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122022216</v>
+        <v>122021281</v>
       </c>
       <c r="B20" t="n">
         <v>98185</v>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2958,14 +2958,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1.1, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586328</v>
+        <v>585956</v>
       </c>
       <c r="R20" t="n">
-        <v>6317238</v>
+        <v>6317492</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -2096,7 +2096,7 @@
         <v>121838432</v>
       </c>
       <c r="B13" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122037669</v>
+        <v>122021281</v>
       </c>
       <c r="B14" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2250,26 +2250,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586190</v>
+        <v>585956</v>
       </c>
       <c r="R14" t="n">
-        <v>6317402</v>
+        <v>6317492</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2296,50 +2302,39 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122037687</v>
+        <v>122021993</v>
       </c>
       <c r="B15" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2348,49 +2343,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586183</v>
+        <v>586192</v>
       </c>
       <c r="R15" t="n">
-        <v>6317427</v>
+        <v>6317434</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2417,40 +2409,29 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2460,7 +2441,7 @@
         <v>122022216</v>
       </c>
       <c r="B16" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2573,10 +2554,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122037739</v>
+        <v>122037669</v>
       </c>
       <c r="B17" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2608,7 +2589,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2621,10 +2602,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586272</v>
+        <v>586190</v>
       </c>
       <c r="R17" t="n">
-        <v>6317286</v>
+        <v>6317402</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2694,10 +2675,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122021993</v>
+        <v>122021641</v>
       </c>
       <c r="B18" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2730,7 +2711,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2739,10 +2720,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586192</v>
+        <v>586088</v>
       </c>
       <c r="R18" t="n">
-        <v>6317434</v>
+        <v>6317479</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2801,10 +2782,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122021641</v>
+        <v>122037687</v>
       </c>
       <c r="B19" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2813,46 +2794,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586088</v>
+        <v>586183</v>
       </c>
       <c r="R19" t="n">
-        <v>6317479</v>
+        <v>6317427</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2879,39 +2863,50 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122021281</v>
+        <v>122037739</v>
       </c>
       <c r="B20" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2943,32 +2938,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585956</v>
+        <v>586272</v>
       </c>
       <c r="R20" t="n">
-        <v>6317492</v>
+        <v>6317286</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2995,29 +2984,40 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
         <v>122058487</v>
       </c>
       <c r="B21" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>122021281</v>
       </c>
       <c r="B14" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021993</v>
+        <v>122037687</v>
       </c>
       <c r="B15" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2343,46 +2343,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586192</v>
+        <v>586183</v>
       </c>
       <c r="R15" t="n">
-        <v>6317434</v>
+        <v>6317427</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2409,39 +2412,50 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122022216</v>
+        <v>122037739</v>
       </c>
       <c r="B16" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,32 +2487,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586328</v>
+        <v>586272</v>
       </c>
       <c r="R16" t="n">
-        <v>6317238</v>
+        <v>6317286</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2525,29 +2533,40 @@
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2557,7 +2576,7 @@
         <v>122037669</v>
       </c>
       <c r="B17" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2675,7 +2694,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122021641</v>
+        <v>122021993</v>
       </c>
       <c r="B18" t="n">
         <v>57395</v>
@@ -2711,7 +2730,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2720,10 +2739,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586088</v>
+        <v>586192</v>
       </c>
       <c r="R18" t="n">
-        <v>6317479</v>
+        <v>6317434</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2782,10 +2801,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122037687</v>
+        <v>122022216</v>
       </c>
       <c r="B19" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2817,26 +2836,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586183</v>
+        <v>586328</v>
       </c>
       <c r="R19" t="n">
-        <v>6317427</v>
+        <v>6317238</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2863,50 +2888,39 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122037739</v>
+        <v>122021641</v>
       </c>
       <c r="B20" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2915,49 +2929,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råsnäs, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586272</v>
+        <v>586088</v>
       </c>
       <c r="R20" t="n">
-        <v>6317286</v>
+        <v>6317479</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2984,40 +2995,29 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -2694,10 +2694,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122021993</v>
+        <v>122022216</v>
       </c>
       <c r="B18" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2706,43 +2706,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
+          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586192</v>
+        <v>586328</v>
       </c>
       <c r="R18" t="n">
-        <v>6317434</v>
+        <v>6317238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2801,10 +2810,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122022216</v>
+        <v>122021993</v>
       </c>
       <c r="B19" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2813,52 +2822,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råsnäs 1:1, Råsnäs 1:1, Sm</t>
+          <t>Råsnäs 1.1, Råsnäs, Timmernabben, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586328</v>
+        <v>586192</v>
       </c>
       <c r="R19" t="n">
-        <v>6317238</v>
+        <v>6317434</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -3042,11 +3042,6 @@
       <c r="E21" t="n">
         <v>100138</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1383,12 +1383,7 @@
         <v>63225984</v>
       </c>
       <c r="B7" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586251.2163676168</v>
+        <v>586251</v>
       </c>
       <c r="R7" t="n">
-        <v>6317339.895135884</v>
+        <v>6317340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1477,19 +1472,9 @@
           <t>2013-06-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-06-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>63225984</v>
       </c>
       <c r="B7" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>63225984</v>
       </c>
       <c r="B7" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61003-2024 artfynd.xlsx
+++ b/artfynd/A 61003-2024 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>63225984</v>
       </c>
       <c r="B7" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
